--- a/artfynd/A 33872-2021 artfynd.xlsx
+++ b/artfynd/A 33872-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33872-2021 artfynd.xlsx
+++ b/artfynd/A 33872-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16612569</v>
+        <v>16612470</v>
       </c>
       <c r="B2" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,45 +686,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ståltorp V  11, Srm</t>
+          <t>Ståltorp V  10, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597655.0766274539</v>
+        <v>597669</v>
       </c>
       <c r="R2" t="n">
-        <v>6549701.908844005</v>
+        <v>6549802</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,24 +754,14 @@
           <t>2014-09-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-09-12</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>3 plantor med 7 blommande ex</t>
+          <t>2 sporkapslar på gammal granlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -803,15 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16612614</v>
+        <v>16612539</v>
       </c>
       <c r="B3" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -819,44 +799,45 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ståltorp V  21, Srm</t>
+          <t>Ståltorp V  11, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597830.9120287222</v>
+        <v>597655</v>
       </c>
       <c r="R3" t="n">
-        <v>6549413.759212832</v>
+        <v>6549702</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,24 +867,14 @@
           <t>2014-09-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2014-09-12</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Grovticka med en diameter på 4dm och i 4 skikt. Vid roten av gammal tall</t>
+          <t>En gammal granlåga med 23 utspridda sporkapslar och ca 15m so en ytterligare låga med en sporkapsel</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,7 +883,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -931,15 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>16612539</v>
+        <v>16612578</v>
       </c>
       <c r="B4" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,7 +931,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -978,14 +943,14 @@
       <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ståltorp V  11, Srm</t>
+          <t>Ståltorp V  13, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597655.0766274539</v>
+        <v>597624</v>
       </c>
       <c r="R4" t="n">
-        <v>6549701.908844005</v>
+        <v>6549636</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1015,24 +980,14 @@
           <t>2014-09-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2014-09-12</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>En gammal granlåga med 23 utspridda sporkapslar och ca 15m so en ytterligare låga med en sporkapsel</t>
+          <t>1 ex på gammal granstubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1059,15 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>16612470</v>
+        <v>16612594</v>
       </c>
       <c r="B5" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,14 +1056,14 @@
       <c r="L5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ståltorp V  10, Srm</t>
+          <t>Ståltorp V  17, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597669.00797752</v>
+        <v>597736</v>
       </c>
       <c r="R5" t="n">
-        <v>6549802.034406123</v>
+        <v>6549495</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1143,24 +1093,14 @@
           <t>2014-09-12</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2014-09-12</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2 sporkapslar på gammal granlåga</t>
+          <t>2 sporkapslar på gammal granstubbe</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1187,15 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>16612618</v>
+        <v>16612605</v>
       </c>
       <c r="B6" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1157,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1234,14 +1169,14 @@
       <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ståltorp V  22, Srm</t>
+          <t>Ståltorp V  19, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597823.8977681777</v>
+        <v>597760</v>
       </c>
       <c r="R6" t="n">
-        <v>6549385.806284534</v>
+        <v>6549480</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1271,24 +1206,14 @@
           <t>2014-09-12</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2014-09-12</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2 sporkapslar på avsågad granlåga</t>
+          <t>7 sporkapslar på gammal granstubbe</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1315,15 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>16612673</v>
+        <v>16612618</v>
       </c>
       <c r="B7" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>210</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1355,21 +1275,21 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ståltorp V  25, Srm</t>
+          <t>Ståltorp V  22, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597689.2151482992</v>
+        <v>597824</v>
       </c>
       <c r="R7" t="n">
-        <v>6549615.864774659</v>
+        <v>6549386</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1399,24 +1319,14 @@
           <t>2014-09-12</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2014-09-12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ca 2 m2 fina små kuddar</t>
+          <t>2 sporkapslar på avsågad granlåga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1443,15 +1353,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>17183006</v>
+        <v>55136542</v>
       </c>
       <c r="B8" t="n">
-        <v>43464</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,39 +1364,45 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101735</v>
+        <v>210</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>SSO Haga, Srm</t>
+          <t>Stålstorp, V om, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597578.8302122337</v>
+        <v>597660</v>
       </c>
       <c r="R8" t="n">
-        <v>6549802.819865272</v>
+        <v>6549798</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1518,27 +1429,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2015-03-04</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-09-09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2015-03-04</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-09-09</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Kläckhål i fnöskticka på björklåga.</t>
+          <t>På gammal rötskadad granlåga. Nyckelbiotop.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1565,15 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>55136542</v>
+        <v>55136556</v>
       </c>
       <c r="B9" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1616,10 +1512,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597659.8324352198</v>
+        <v>597628</v>
       </c>
       <c r="R9" t="n">
-        <v>6549798.20036148</v>
+        <v>6549763</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1649,24 +1545,14 @@
           <t>2015-09-09</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2015-09-09</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gammal rötskadad granlåga. Nyckelbiotop.</t>
+          <t>På gammal rötskadad tallåga. Befintlig nyckelbiotop.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1693,37 +1579,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>55136625</v>
+        <v>16623123</v>
       </c>
       <c r="B10" t="n">
-        <v>88853</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4189</v>
+        <v>1445</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1739,17 +1620,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stålstorp, V om, Srm</t>
+          <t>Stålstorp, S om, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597679.7541502063</v>
+        <v>597578</v>
       </c>
       <c r="R10" t="n">
-        <v>6549724.138484765</v>
+        <v>6549731</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1773,27 +1654,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2015-09-09</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-03-05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2015-09-09</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Fjolårsex i barrmattan under gammal gran. Nyckelbiotop.</t>
+          <t>2014-03-05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1821,55 +1687,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>55136505</v>
+        <v>17151804</v>
       </c>
       <c r="B11" t="n">
-        <v>88902</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5734</v>
+        <v>1445</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Druvfingersvamp</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramaria botrytis</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bourdot</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stålstorp, V om, Srm</t>
+          <t>stålstorp-falkenbo, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597616.9685780962</v>
+        <v>597770</v>
       </c>
       <c r="R11" t="n">
-        <v>6549802.249589803</v>
+        <v>6549377</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1893,27 +1758,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2015-09-09</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-02-27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2015-09-09</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Sluttning med gammal grandominerad skog. Befintlig nyckelbiotop.</t>
+          <t>2015-02-27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1929,64 +1779,67 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Patrick Björck</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Patrick Björck</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>55136485</v>
+        <v>17183000</v>
       </c>
       <c r="B12" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5964</v>
+        <v>1445</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stålstorp, V om, Srm</t>
+          <t>SSO Haga, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597587.8447787329</v>
+        <v>597580</v>
       </c>
       <c r="R12" t="n">
-        <v>6549792.764264317</v>
+        <v>6549735</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2013,22 +1866,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2015-09-09</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-03-04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2015-09-09</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-03-04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På en yta av ca 10 x 15m. Gammal granskog i anslutning till svag nordsluttning vid åsrygg. Öster om fastighetsgräns.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2056,55 +1904,55 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>55136588</v>
+        <v>17183008</v>
       </c>
       <c r="B13" t="n">
-        <v>43464</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>101735</v>
+        <v>1445</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stålstorp, V om, Srm</t>
+          <t>SSV Stålstorp, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597723.8941598986</v>
+        <v>597720</v>
       </c>
       <c r="R13" t="n">
-        <v>6549771.036135193</v>
+        <v>6549503</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2131,27 +1979,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2015-09-09</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-03-04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2015-09-09</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-03-04</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Kläckhål i fnösktickor på gammal björkhögstubbe.</t>
+          <t>Äldre granskog i nordostvänd sluttning. På en yta av ca 20x30m.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2160,6 +1998,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2178,53 +2017,55 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>88405507</v>
+        <v>17183018</v>
       </c>
       <c r="B14" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5964</v>
+        <v>1445</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stålstorp, V om, Srm</t>
+          <t>SSV Stålstorp, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597589.8779830815</v>
+        <v>597756</v>
       </c>
       <c r="R14" t="n">
-        <v>6549793.84465194</v>
+        <v>6549473</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2251,22 +2092,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2020-09-30</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-03-04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2020-09-30</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-03-04</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre granskog i anslutning till nordostvänd sluttning.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2291,6 +2127,2615 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>17183041</v>
+      </c>
+      <c r="B15" t="n">
+        <v>84158</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>SSV Stålstorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>597764</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6549474</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Helgesta</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2015-03-04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2015-03-04</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>17183064</v>
+      </c>
+      <c r="B16" t="n">
+        <v>84158</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>SSV Stålstorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>597777</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6549459</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Helgesta</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2015-03-04</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2015-03-04</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>57755441</v>
+      </c>
+      <c r="B17" t="n">
+        <v>84158</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Stålstorp, V om, Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>597626</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6549697</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Helgesta</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2016-03-22</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2016-03-22</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Nyckelbiotop.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>57755461</v>
+      </c>
+      <c r="B18" t="n">
+        <v>84158</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Stålstorp, V om, Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>597601</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6549771</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Helgesta</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2016-03-22</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2016-03-22</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Nyckelbiotop.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>16612599</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91333</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2008</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Fyrflikig jordstjärna</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Geastrum quadrifidum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Pers., nom.sanct.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ståltorp V  18, Srm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>597736</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6549493</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Helgesta</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2014-09-12</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2014-09-12</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>5 fjolårsex vid gammal gran</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>16612673</v>
+      </c>
+      <c r="B20" t="n">
+        <v>96708</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ståltorp V  25, Srm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>597689</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6549616</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Helgesta</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2014-09-12</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2014-09-12</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>ca 2 m2 fina små kuddar</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>16612600</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4189</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Kamjordstjärna</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Geastrum pectinatum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Pers., nom.sanct</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Ståltorp V  18, Srm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>597736</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6549493</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Helgesta</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2014-09-12</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2014-09-12</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>1 fjolårsex vid gammal gran</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>55136625</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4189</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Kamjordstjärna</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Geastrum pectinatum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Pers., nom.sanct</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Stålstorp, V om, Srm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>597680</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6549724</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Helgesta</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2015-09-09</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2015-09-09</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Fjolårsex i barrmattan under gammal gran. Nyckelbiotop.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>16612603</v>
+      </c>
+      <c r="B23" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Ståltorp V  18, Srm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>597736</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6549493</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Helgesta</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2014-09-12</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2014-09-12</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>16612614</v>
+      </c>
+      <c r="B24" t="n">
+        <v>92348</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5420</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Ståltorp V  21, Srm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>597831</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6549414</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Helgesta</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2014-09-12</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2014-09-12</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Grovticka med en diameter på 4dm och i 4 skikt. Vid roten av gammal tall</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>55136485</v>
+      </c>
+      <c r="B25" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Stålstorp, V om, Srm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>597588</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6549793</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Helgesta</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2015-09-09</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2015-09-09</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>88405507</v>
+      </c>
+      <c r="B26" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Stålstorp, V om, Srm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>597590</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6549794</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Helgesta</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2020-09-30</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2020-09-30</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>17183006</v>
+      </c>
+      <c r="B27" t="n">
+        <v>44177</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>SSO Haga, Srm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>597579</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6549803</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Helgesta</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2015-03-04</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2015-03-04</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Kläckhål i fnöskticka på björklåga.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>55136588</v>
+      </c>
+      <c r="B28" t="n">
+        <v>44177</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Stålstorp, V om, Srm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>597724</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6549771</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Helgesta</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2015-09-09</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2015-09-09</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Kläckhål i fnösktickor på gammal björkhögstubbe.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>88405435</v>
+      </c>
+      <c r="B29" t="n">
+        <v>44177</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Stålstorp, V om, Srm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>597603</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6549561</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Helgesta</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2020-09-30</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2020-09-30</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Larv i fnöskticka på björklåga.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>95390492</v>
+      </c>
+      <c r="B30" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Stålstorp 200m ssv, Srm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>597823</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6549508</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Helgesta</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2021-08-09</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2021-08-09</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Skogsbryn</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>16612363</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Ståltorp V  6, Srm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>597628</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6549697</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Helgesta</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2014-09-12</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2014-09-12</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>ca 0,5 m2 marktäckning och 5 ex i blom</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>71202698</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Stålstorp, V om, Srm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>597638</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6549650</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Helgesta</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2018-05-06</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2018-05-06</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>88405504</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Stålstorp, V om, Srm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>597647</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6549653</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Helgesta</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2020-09-30</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2020-09-30</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>91833304</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Stålstorp, skog V om, Srm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>597624</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6549704</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Helgesta</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2021-03-23</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2021-03-23</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>granskog</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>92778357</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Stålstorp, V om, Srm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>597595</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6549750</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Helgesta</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2021-04-26</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2021-04-26</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ett litet skott i anslutning till grisbök.</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>16612569</v>
+      </c>
+      <c r="B36" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Ståltorp V  11, Srm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>597655</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6549702</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Helgesta</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2014-09-12</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2014-09-12</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>3 plantor med 7 blommande ex</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>17183009</v>
+      </c>
+      <c r="B37" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>SSV Stålstorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>597720</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6549503</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Helgesta</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2015-03-04</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2015-03-04</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>95390509</v>
+      </c>
+      <c r="B38" t="n">
+        <v>101746</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>224932</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vanlig backsmörblomma</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Ranunculus polyanthemos subsp. polyanthemos</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Stålstorp 200m ssv, Srm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>597823</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6549508</v>
+      </c>
+      <c r="S38" t="n">
+        <v>25</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Helgesta</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2021-08-09</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2021-08-09</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Skogsbryn</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
